--- a/MainTop/25.03.2026 Таня Озон/print_print_sorted.xlsx
+++ b/MainTop/25.03.2026 Таня Озон/print_print_sorted.xlsx
@@ -5,17 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\25.03.2026 Таня Озон\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\25.03.2026 Таня Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCD688D-2C7A-4D62-AF1F-F7D2870B0E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D2EF96-BB98-42F4-80AD-6B3A9C8D3FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -476,10 +487,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -785,7 +796,19 @@
   <dimension ref="A1:N107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="49.7109375" customWidth="1"/>
+    <col min="1" max="1" width="39.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" customWidth="1"/>
+    <col min="3" max="3" width="6.28515625" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" customWidth="1"/>
+    <col min="5" max="5" width="5.85546875" customWidth="1"/>
+    <col min="6" max="7" width="5.28515625" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" customWidth="1"/>
+    <col min="9" max="9" width="5" customWidth="1"/>
+    <col min="10" max="10" width="5.42578125" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="5" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" customWidth="1"/>
+    <col min="14" max="14" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -5498,5 +5521,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>